--- a/artfynd/A 35164-2025 artfynd.xlsx
+++ b/artfynd/A 35164-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -792,6 +792,306 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>127443999</v>
+      </c>
+      <c r="B3" t="n">
+        <v>91344</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Långgrunden, Vb</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>801795</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7178280</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>127444000</v>
+      </c>
+      <c r="B4" t="n">
+        <v>91344</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Långgrunden, Vb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>801725</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7178253</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>127443997</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91692</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>2064</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Kilporing</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Skeletocutis kuehneri</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>A.David</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Långgrunden, Vb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>801756</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7178255</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Växte på och bredvid döda violtickor. Luktade mycket tydligt Skeletocutis. Karaktärererna och ekologin stämmer bra med kilporing utifrån PFoE. Tog kollekt.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 35164-2025 artfynd.xlsx
+++ b/artfynd/A 35164-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1093,6 +1093,216 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>127471685</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91344</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5432</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Granticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Porodaedalea chrysoloma</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Tällöuttingen, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>801751</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7178270</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>127471833</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91322</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1108</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Harticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Tällöuttingen, Vb</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>801808</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7178279</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Bureå</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-08-11</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35164-2025 artfynd.xlsx
+++ b/artfynd/A 35164-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>127443999</v>
       </c>
       <c r="B3" t="n">
-        <v>91344</v>
+        <v>91348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>127444000</v>
       </c>
       <c r="B4" t="n">
-        <v>91344</v>
+        <v>91348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>127443997</v>
       </c>
       <c r="B5" t="n">
-        <v>91692</v>
+        <v>91696</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>127471685</v>
       </c>
       <c r="B6" t="n">
-        <v>91344</v>
+        <v>91348</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>127471833</v>
       </c>
       <c r="B7" t="n">
-        <v>91322</v>
+        <v>91326</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 35164-2025 artfynd.xlsx
+++ b/artfynd/A 35164-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>127443999</v>
       </c>
       <c r="B3" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>127444000</v>
       </c>
       <c r="B4" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>127443997</v>
       </c>
       <c r="B5" t="n">
-        <v>91696</v>
+        <v>91698</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>127471685</v>
       </c>
       <c r="B6" t="n">
-        <v>91348</v>
+        <v>91350</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>127471833</v>
       </c>
       <c r="B7" t="n">
-        <v>91326</v>
+        <v>91328</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 35164-2025 artfynd.xlsx
+++ b/artfynd/A 35164-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>127443999</v>
       </c>
       <c r="B3" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>127444000</v>
       </c>
       <c r="B4" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>127443997</v>
       </c>
       <c r="B5" t="n">
-        <v>91698</v>
+        <v>91704</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>127471685</v>
       </c>
       <c r="B6" t="n">
-        <v>91350</v>
+        <v>91356</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>127471833</v>
       </c>
       <c r="B7" t="n">
-        <v>91328</v>
+        <v>91334</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 35164-2025 artfynd.xlsx
+++ b/artfynd/A 35164-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>127443999</v>
       </c>
       <c r="B3" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>127444000</v>
       </c>
       <c r="B4" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>127443997</v>
       </c>
       <c r="B5" t="n">
-        <v>91704</v>
+        <v>91707</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>127471685</v>
       </c>
       <c r="B6" t="n">
-        <v>91356</v>
+        <v>91359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>127471833</v>
       </c>
       <c r="B7" t="n">
-        <v>91334</v>
+        <v>91337</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 35164-2025 artfynd.xlsx
+++ b/artfynd/A 35164-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>127443999</v>
       </c>
       <c r="B3" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>127444000</v>
       </c>
       <c r="B4" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>127443997</v>
       </c>
       <c r="B5" t="n">
-        <v>91707</v>
+        <v>91715</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>127471685</v>
       </c>
       <c r="B6" t="n">
-        <v>91359</v>
+        <v>91367</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>127471833</v>
       </c>
       <c r="B7" t="n">
-        <v>91337</v>
+        <v>91345</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 35164-2025 artfynd.xlsx
+++ b/artfynd/A 35164-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>127443999</v>
       </c>
       <c r="B3" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>127444000</v>
       </c>
       <c r="B4" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>127443997</v>
       </c>
       <c r="B5" t="n">
-        <v>91715</v>
+        <v>91716</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>127471685</v>
       </c>
       <c r="B6" t="n">
-        <v>91367</v>
+        <v>91368</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>127471833</v>
       </c>
       <c r="B7" t="n">
-        <v>91345</v>
+        <v>91346</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 35164-2025 artfynd.xlsx
+++ b/artfynd/A 35164-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>127443999</v>
       </c>
       <c r="B3" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>127444000</v>
       </c>
       <c r="B4" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>127443997</v>
       </c>
       <c r="B5" t="n">
-        <v>91716</v>
+        <v>91717</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>127471685</v>
       </c>
       <c r="B6" t="n">
-        <v>91368</v>
+        <v>91369</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>127471833</v>
       </c>
       <c r="B7" t="n">
-        <v>91346</v>
+        <v>91347</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 35164-2025 artfynd.xlsx
+++ b/artfynd/A 35164-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>127443999</v>
       </c>
       <c r="B3" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>127444000</v>
       </c>
       <c r="B4" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>127443997</v>
       </c>
       <c r="B5" t="n">
-        <v>91717</v>
+        <v>91718</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>127471685</v>
       </c>
       <c r="B6" t="n">
-        <v>91369</v>
+        <v>91370</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1203,7 +1203,7 @@
         <v>127471833</v>
       </c>
       <c r="B7" t="n">
-        <v>91347</v>
+        <v>91348</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 35164-2025 artfynd.xlsx
+++ b/artfynd/A 35164-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>127443999</v>
       </c>
       <c r="B3" t="n">
-        <v>91370</v>
+        <v>91522</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,14 +888,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>127444000</v>
       </c>
       <c r="B4" t="n">
-        <v>91370</v>
+        <v>91522</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -985,14 +989,18 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>127443997</v>
       </c>
       <c r="B5" t="n">
-        <v>91718</v>
+        <v>91870</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1091,7 +1099,11 @@
           <t>Anton Lundberg</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">

--- a/artfynd/A 35164-2025 artfynd.xlsx
+++ b/artfynd/A 35164-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>127443999</v>
       </c>
       <c r="B3" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>127444000</v>
       </c>
       <c r="B4" t="n">
-        <v>91522</v>
+        <v>91526</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>127443997</v>
       </c>
       <c r="B5" t="n">
-        <v>91870</v>
+        <v>91874</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35164-2025 artfynd.xlsx
+++ b/artfynd/A 35164-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>127443999</v>
       </c>
       <c r="B3" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>127444000</v>
       </c>
       <c r="B4" t="n">
-        <v>91526</v>
+        <v>91531</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>127443997</v>
       </c>
       <c r="B5" t="n">
-        <v>91874</v>
+        <v>91879</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35164-2025 artfynd.xlsx
+++ b/artfynd/A 35164-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>127443999</v>
       </c>
       <c r="B3" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>127444000</v>
       </c>
       <c r="B4" t="n">
-        <v>91538</v>
+        <v>91541</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>127443997</v>
       </c>
       <c r="B5" t="n">
-        <v>91887</v>
+        <v>91890</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35164-2025 artfynd.xlsx
+++ b/artfynd/A 35164-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>127443999</v>
       </c>
       <c r="B3" t="n">
-        <v>91541</v>
+        <v>91544</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>127444000</v>
       </c>
       <c r="B4" t="n">
-        <v>91541</v>
+        <v>91544</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>127443997</v>
       </c>
       <c r="B5" t="n">
-        <v>91890</v>
+        <v>91893</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35164-2025 artfynd.xlsx
+++ b/artfynd/A 35164-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>127443999</v>
       </c>
       <c r="B3" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>127444000</v>
       </c>
       <c r="B4" t="n">
-        <v>91544</v>
+        <v>91551</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>127443997</v>
       </c>
       <c r="B5" t="n">
-        <v>91893</v>
+        <v>91900</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35164-2025 artfynd.xlsx
+++ b/artfynd/A 35164-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>127443999</v>
       </c>
       <c r="B3" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>127444000</v>
       </c>
       <c r="B4" t="n">
-        <v>91551</v>
+        <v>91558</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>127443997</v>
       </c>
       <c r="B5" t="n">
-        <v>91900</v>
+        <v>91907</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35164-2025 artfynd.xlsx
+++ b/artfynd/A 35164-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>127443999</v>
       </c>
       <c r="B3" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>127444000</v>
       </c>
       <c r="B4" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>127443997</v>
       </c>
       <c r="B5" t="n">
-        <v>91907</v>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35164-2025 artfynd.xlsx
+++ b/artfynd/A 35164-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>127443999</v>
       </c>
       <c r="B3" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>127444000</v>
       </c>
       <c r="B4" t="n">
-        <v>91560</v>
+        <v>91558</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1000,7 +1000,7 @@
         <v>127443997</v>
       </c>
       <c r="B5" t="n">
-        <v>91909</v>
+        <v>91918</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35164-2025 artfynd.xlsx
+++ b/artfynd/A 35164-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>127443999</v>
       </c>
       <c r="B3" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -815,14 +815,10 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -899,7 +895,7 @@
         <v>127444000</v>
       </c>
       <c r="B4" t="n">
-        <v>91558</v>
+        <v>91560</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -916,14 +912,10 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
+          <t>Porodaedalea chrysoloma s.lat.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1000,7 +992,7 @@
         <v>127443997</v>
       </c>
       <c r="B5" t="n">
-        <v>91918</v>
+        <v>91919</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35164-2025 artfynd.xlsx
+++ b/artfynd/A 35164-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>127443999</v>
       </c>
       <c r="B3" t="n">
-        <v>91560</v>
+        <v>91563</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>127444000</v>
       </c>
       <c r="B4" t="n">
-        <v>91560</v>
+        <v>91563</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>127443997</v>
       </c>
       <c r="B5" t="n">
-        <v>91919</v>
+        <v>91922</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35164-2025 artfynd.xlsx
+++ b/artfynd/A 35164-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>127443999</v>
       </c>
       <c r="B3" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>127444000</v>
       </c>
       <c r="B4" t="n">
-        <v>91563</v>
+        <v>91565</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>127443997</v>
       </c>
       <c r="B5" t="n">
-        <v>91922</v>
+        <v>91924</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35164-2025 artfynd.xlsx
+++ b/artfynd/A 35164-2025 artfynd.xlsx
@@ -798,7 +798,7 @@
         <v>127443999</v>
       </c>
       <c r="B3" t="n">
-        <v>91565</v>
+        <v>91569</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -895,7 +895,7 @@
         <v>127444000</v>
       </c>
       <c r="B4" t="n">
-        <v>91565</v>
+        <v>91569</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>127443997</v>
       </c>
       <c r="B5" t="n">
-        <v>91924</v>
+        <v>91928</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 35164-2025 artfynd.xlsx
+++ b/artfynd/A 35164-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>106153116</v>
       </c>
       <c r="B2" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -700,12 +695,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -722,10 +717,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>801712.0607842887</v>
+        <v>801712</v>
       </c>
       <c r="R2" t="n">
-        <v>7178283.69187462</v>
+        <v>7178284</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,19 +750,9 @@
           <t>2019-09-11</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-09-11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,10 +780,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127443999</v>
+        <v>127471833</v>
       </c>
       <c r="B3" t="n">
-        <v>91569</v>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -806,30 +791,41 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
+          <t>Pelloporus leporinus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Långgrunden, Vb</t>
+          <t>Tällöuttingen, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>801795</v>
+        <v>801808</v>
       </c>
       <c r="R3" t="n">
-        <v>7178280</v>
+        <v>7178279</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -870,63 +866,67 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127444000</v>
+        <v>127443997</v>
       </c>
       <c r="B4" t="n">
-        <v>91569</v>
+        <v>92289</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>2064</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Kilporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma s.lat.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
+          <t>Skeletocutis kuehneri</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>A.David</t>
+        </is>
+      </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Långgrunden, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>801725</v>
+        <v>801756</v>
       </c>
       <c r="R4" t="n">
-        <v>7178253</v>
+        <v>7178255</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -961,12 +961,18 @@
           <t>2025-08-11</t>
         </is>
       </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Växte på och bredvid döda violtickor. Luktade mycket tydligt Skeletocutis. Karaktärererna och ekologin stämmer bra med kilporing utifrån PFoE. Tog kollekt.</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -986,326 +992,6 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>127443997</v>
-      </c>
-      <c r="B5" t="n">
-        <v>91928</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>2064</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Kilporing</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Skeletocutis kuehneri</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>A.David</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Långgrunden, Vb</t>
-        </is>
-      </c>
-      <c r="Q5" t="n">
-        <v>801756</v>
-      </c>
-      <c r="R5" t="n">
-        <v>7178255</v>
-      </c>
-      <c r="S5" t="n">
-        <v>10</v>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Skellefteå</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>Bureå</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2025-08-11</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>2025-08-11</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Växte på och bredvid döda violtickor. Luktade mycket tydligt Skeletocutis. Karaktärererna och ekologin stämmer bra med kilporing utifrån PFoE. Tog kollekt.</t>
-        </is>
-      </c>
-      <c r="AD5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="inlineStr"/>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>Anton Lundberg</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>127471685</v>
-      </c>
-      <c r="B6" t="n">
-        <v>91370</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Tällöuttingen, Vb</t>
-        </is>
-      </c>
-      <c r="Q6" t="n">
-        <v>801751</v>
-      </c>
-      <c r="R6" t="n">
-        <v>7178270</v>
-      </c>
-      <c r="S6" t="n">
-        <v>10</v>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Skellefteå</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>Bureå</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>2025-08-11</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>2025-08-11</t>
-        </is>
-      </c>
-      <c r="AD6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="inlineStr"/>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>Patrik Nygren</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>Patrik Nygren</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>127471833</v>
-      </c>
-      <c r="B7" t="n">
-        <v>91348</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>1108</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Harticka</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Pelloporus leporinus</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Fr.) Krieglst.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Tällöuttingen, Vb</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>801808</v>
-      </c>
-      <c r="R7" t="n">
-        <v>7178279</v>
-      </c>
-      <c r="S7" t="n">
-        <v>10</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Skellefteå</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Västerbotten</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Bureå</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2025-08-11</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2025-08-11</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Patrik Nygren</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Patrik Nygren</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 35164-2025 artfynd.xlsx
+++ b/artfynd/A 35164-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106153116</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127471833</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1012,8 +1027,18 @@
           <t>Naturskyddsföreningen i Västerbottens naturvärdesinventeringar 2025</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127443997</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 35164-2025 artfynd.xlsx
+++ b/artfynd/A 35164-2025 artfynd.xlsx
@@ -903,7 +903,7 @@
         <v>127443997</v>
       </c>
       <c r="B4" t="n">
-        <v>92326</v>
+        <v>92368</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
